--- a/docs/templates/B5C3-SHORE.xlsx
+++ b/docs/templates/B5C3-SHORE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A37F4BB9-5E3E-4D98-A2DD-5C0AC41F8808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDD2A934-DA82-4788-98FC-7DB2FE11A42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2CFD503A-6F8A-4F29-BFA6-F7B55C77A07B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{29C08244-6CAE-42EF-8B83-29AF5A6494FC}"/>
   </bookViews>
   <sheets>
     <sheet name="DataImport" sheetId="1" r:id="rId1"/>
@@ -1048,62 +1048,62 @@
     </xf>
   </cellXfs>
   <cellStyles count="56">
-    <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{6314F675-F983-4270-BEDF-436ECE6C86A1}"/>
+    <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{2A61075E-6F51-4970-A69D-296CD5685116}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="2" xr:uid="{FE5153DC-F467-44D1-8BBE-B5DC196ED19B}"/>
-    <cellStyle name="Normal 10 10" xfId="3" xr:uid="{8755B3A2-4E79-4220-BF78-A27D01B17B76}"/>
-    <cellStyle name="Normal 10 10 2" xfId="4" xr:uid="{668767FE-9DA2-48F4-83A9-49497ECFCB69}"/>
-    <cellStyle name="Normal 10 2 10" xfId="5" xr:uid="{8996E127-7294-4D39-A4E5-0B5EB6DE0A93}"/>
-    <cellStyle name="Normal 12" xfId="6" xr:uid="{F1F26907-1226-473A-B4C9-757993C64AF7}"/>
-    <cellStyle name="Normal 13" xfId="7" xr:uid="{485F5E87-AEDC-41A3-B95E-FBACEADBF262}"/>
-    <cellStyle name="Normal 137" xfId="8" xr:uid="{0C29DD15-0EFB-4AE3-ADC9-9119061F00B8}"/>
-    <cellStyle name="Normal 14" xfId="9" xr:uid="{C245A371-45CF-4A05-B9A9-FBEFCEF83680}"/>
-    <cellStyle name="Normal 15" xfId="10" xr:uid="{905481A0-F312-465A-85B0-558DB0D78C6D}"/>
-    <cellStyle name="Normal 2" xfId="11" xr:uid="{0461EC14-3E59-46CF-A13B-AFF0E3E014A0}"/>
-    <cellStyle name="Normal 2 10" xfId="12" xr:uid="{9B4AC9C2-FC80-4B62-A4F6-01DA328C03A0}"/>
-    <cellStyle name="Normal 2 10 2" xfId="13" xr:uid="{30CE86D3-7440-49DB-A950-688FED29BB91}"/>
-    <cellStyle name="Normal 2 10 2 2" xfId="14" xr:uid="{C1377E0A-74CB-40BE-AC6A-7CDE0EB03B93}"/>
-    <cellStyle name="Normal 2 2" xfId="15" xr:uid="{1FA91F00-3945-4F14-8544-A39BCAF89167}"/>
-    <cellStyle name="Normal 2 2 10" xfId="16" xr:uid="{99022B39-A1A9-4832-8894-A806661C2B96}"/>
-    <cellStyle name="Normal 2 2 2" xfId="17" xr:uid="{77A78D8C-9901-4554-BFA2-0E32E642EEC0}"/>
-    <cellStyle name="Normal 2 2 3" xfId="18" xr:uid="{CD5AB376-303C-47B9-AC22-E6A8F5C44092}"/>
-    <cellStyle name="Normal 2 3" xfId="19" xr:uid="{E5BCCC21-0DB5-49F5-8C43-99DA8304E717}"/>
-    <cellStyle name="Normal 2 4" xfId="20" xr:uid="{9D1FD276-E920-4548-8BE7-851E4DC0FB12}"/>
-    <cellStyle name="Normal 2 5" xfId="21" xr:uid="{D13CE737-FB6E-468F-89B8-CCE73DAF128B}"/>
-    <cellStyle name="Normal 3" xfId="22" xr:uid="{0A476F52-9498-4998-9C73-050945D05638}"/>
-    <cellStyle name="Normal 3 2" xfId="23" xr:uid="{F6EA7D14-DB88-427F-86EB-1C221DEC41C8}"/>
-    <cellStyle name="Normal 4" xfId="24" xr:uid="{A81E54B8-0C77-4CB5-9513-2B7092CB5BAB}"/>
-    <cellStyle name="Normal 49" xfId="25" xr:uid="{EC29AC5B-699D-49AF-9198-C80DBBDF8599}"/>
-    <cellStyle name="Normal 5" xfId="26" xr:uid="{32E83FF2-0C04-4D23-87B4-381D24AD4595}"/>
-    <cellStyle name="Normal 53" xfId="27" xr:uid="{6C23DD0D-587D-4E6B-A133-0465009747AC}"/>
-    <cellStyle name="Normal 54" xfId="28" xr:uid="{0E3180BB-F8EB-48B0-9D29-FD8FC6F97D2C}"/>
-    <cellStyle name="Normal 6" xfId="29" xr:uid="{B37DD875-E392-4343-979F-8CFDF0F90539}"/>
-    <cellStyle name="Normal 7" xfId="30" xr:uid="{8E5FAFBF-3E4C-4161-B3AA-D4B9BB8D04AA}"/>
-    <cellStyle name="Normal 71" xfId="31" xr:uid="{C6C7FB11-8E11-4FF3-A04B-364F2A02E024}"/>
-    <cellStyle name="Normal 8" xfId="32" xr:uid="{47028D1A-3FCB-4EE8-AF5D-75D5C0BED9D6}"/>
-    <cellStyle name="Normal 9" xfId="33" xr:uid="{2576E837-FA6B-4E35-8E0A-3DFE46C2E4EB}"/>
+    <cellStyle name="Normal 10" xfId="2" xr:uid="{97BEBB86-E161-4B05-8D19-574CBB1278F3}"/>
+    <cellStyle name="Normal 10 10" xfId="3" xr:uid="{050E772B-CC1B-47B6-8252-ACBAEB33A670}"/>
+    <cellStyle name="Normal 10 10 2" xfId="4" xr:uid="{34309A6A-B7F8-498E-AE2A-47A300B97B31}"/>
+    <cellStyle name="Normal 10 2 10" xfId="5" xr:uid="{0ECEABAE-1E2A-4A8C-A631-2ACA4BE6AD35}"/>
+    <cellStyle name="Normal 12" xfId="6" xr:uid="{360AF68B-F1AD-4078-9332-BE8FB73C6327}"/>
+    <cellStyle name="Normal 13" xfId="7" xr:uid="{7D5776B5-A70C-4662-8382-5443107DF926}"/>
+    <cellStyle name="Normal 137" xfId="8" xr:uid="{51198212-6EB1-49E1-9F87-AD3ABE351AEF}"/>
+    <cellStyle name="Normal 14" xfId="9" xr:uid="{69542323-933E-4B2A-8DBD-46E3093BE67C}"/>
+    <cellStyle name="Normal 15" xfId="10" xr:uid="{524D18C0-D358-4123-9BB8-C03B282F8975}"/>
+    <cellStyle name="Normal 2" xfId="11" xr:uid="{5CD0976C-D9A3-48EC-AE07-E44225E9D193}"/>
+    <cellStyle name="Normal 2 10" xfId="12" xr:uid="{4928F55C-926C-448B-B54F-2A58452DDD50}"/>
+    <cellStyle name="Normal 2 10 2" xfId="13" xr:uid="{3F10BAEF-953A-47DF-A051-7C2B303A81F8}"/>
+    <cellStyle name="Normal 2 10 2 2" xfId="14" xr:uid="{90FA1FA6-4A97-425F-8A36-645E53CE5651}"/>
+    <cellStyle name="Normal 2 2" xfId="15" xr:uid="{3DC818D3-517D-481D-821A-3E5AC1A2915E}"/>
+    <cellStyle name="Normal 2 2 10" xfId="16" xr:uid="{C8F13628-D0DD-41F0-90E4-DE3C2FFFDDEF}"/>
+    <cellStyle name="Normal 2 2 2" xfId="17" xr:uid="{6B809E5F-057D-4249-9F44-77D23ABD8A3F}"/>
+    <cellStyle name="Normal 2 2 3" xfId="18" xr:uid="{84CC8274-047A-48EF-8DB8-5BEBAA8341CF}"/>
+    <cellStyle name="Normal 2 3" xfId="19" xr:uid="{C3E60231-0A87-4891-87E0-EAB66D1DFB44}"/>
+    <cellStyle name="Normal 2 4" xfId="20" xr:uid="{6AF4C6E1-07D2-4D1C-8331-08A6437725F9}"/>
+    <cellStyle name="Normal 2 5" xfId="21" xr:uid="{E84D4329-8091-4A08-9A0C-0D1B901971B8}"/>
+    <cellStyle name="Normal 3" xfId="22" xr:uid="{98AC802A-5B69-4FEC-9DCF-88BAD0C28640}"/>
+    <cellStyle name="Normal 3 2" xfId="23" xr:uid="{88154D28-911A-4825-A435-8E2E3746101D}"/>
+    <cellStyle name="Normal 4" xfId="24" xr:uid="{CC01170A-D9DC-45AE-B934-0DF3F22498FA}"/>
+    <cellStyle name="Normal 49" xfId="25" xr:uid="{80EF221E-D9C1-4994-A059-82E15CBF03A1}"/>
+    <cellStyle name="Normal 5" xfId="26" xr:uid="{6EAB46B3-D5CA-4F01-844E-6062034B665C}"/>
+    <cellStyle name="Normal 53" xfId="27" xr:uid="{0790E3D8-4B69-4944-8ECB-AB74C7A25D52}"/>
+    <cellStyle name="Normal 54" xfId="28" xr:uid="{AEA235E2-9A94-4F0E-B959-43A8777EF102}"/>
+    <cellStyle name="Normal 6" xfId="29" xr:uid="{53166880-C3FD-496B-9FA8-95D98AA0A440}"/>
+    <cellStyle name="Normal 7" xfId="30" xr:uid="{90CD75FC-64DD-475B-B957-0BC8DDC477FD}"/>
+    <cellStyle name="Normal 71" xfId="31" xr:uid="{6105A732-DA9D-416D-92AA-F98F73A49A57}"/>
+    <cellStyle name="Normal 8" xfId="32" xr:uid="{445465AA-951A-4568-8D6F-48198A1E5FEC}"/>
+    <cellStyle name="Normal 9" xfId="33" xr:uid="{3DEF6BD9-FB35-4925-BEE3-D4869137AA4C}"/>
     <cellStyle name="Percent" xfId="34" builtinId="5"/>
-    <cellStyle name="จุลภาค 2" xfId="35" xr:uid="{EF679910-A73C-492A-9A01-27C6D12CDE8B}"/>
-    <cellStyle name="ปกติ 10" xfId="36" xr:uid="{B7501956-9C1F-4548-92EF-0A17D962BC26}"/>
-    <cellStyle name="ปกติ 11" xfId="37" xr:uid="{6E203D2F-6E39-4343-B1F0-BBAE0DAAC8F3}"/>
-    <cellStyle name="ปกติ 12" xfId="38" xr:uid="{5B3EAA8B-06A9-4551-9B5D-CDEED30BBCBF}"/>
-    <cellStyle name="ปกติ 13" xfId="39" xr:uid="{33BCEB13-D97B-4D3B-A8D9-DB21F6740124}"/>
-    <cellStyle name="ปกติ 2" xfId="40" xr:uid="{C5CFE923-7DD5-4FCE-B59D-DC371A040CC8}"/>
-    <cellStyle name="ปกติ 2 2" xfId="41" xr:uid="{BA3C2D47-387A-4E95-90BF-050F1DCB5040}"/>
-    <cellStyle name="ปกติ 2 3" xfId="42" xr:uid="{0AE924B5-9EB4-4C86-B5E5-04E4C4282A8F}"/>
-    <cellStyle name="ปกติ 2 4" xfId="43" xr:uid="{2F6265B4-A9AF-4DDC-8A09-B0CB508128C4}"/>
-    <cellStyle name="ปกติ 2 5" xfId="44" xr:uid="{848866A4-233E-4668-9D1D-582E6443B5FB}"/>
-    <cellStyle name="ปกติ 21" xfId="45" xr:uid="{218AC449-5B34-4EDC-8FD5-EAE53966801E}"/>
-    <cellStyle name="ปกติ 29" xfId="46" xr:uid="{9AB6F768-8E13-48C8-B541-E7B3E2203FCA}"/>
-    <cellStyle name="ปกติ 3" xfId="47" xr:uid="{D10D5B09-E108-4E38-AC43-B0EBFFC1A341}"/>
-    <cellStyle name="ปกติ 4" xfId="48" xr:uid="{4043EDDB-BAB8-457D-AB57-9508C544A6CC}"/>
-    <cellStyle name="ปกติ 5" xfId="49" xr:uid="{46CDC9E9-A878-4A61-95A8-91FDBB4DF6C4}"/>
-    <cellStyle name="ปกติ 6" xfId="50" xr:uid="{ABAF83C3-9F9C-47B8-8B2D-F434618FCEB9}"/>
-    <cellStyle name="ปกติ 61" xfId="51" xr:uid="{F8A9F86C-CF02-439B-98C9-D4C03AFBEC96}"/>
-    <cellStyle name="ปกติ 7" xfId="52" xr:uid="{34FD8B4F-6D71-42F1-85C1-AD17B0ED130C}"/>
-    <cellStyle name="ปกติ 8" xfId="53" xr:uid="{F44F67C3-5AB3-4BBB-A63D-B2CF398E9927}"/>
-    <cellStyle name="ปกติ 9" xfId="54" xr:uid="{0A6D2CB3-EA27-4E03-9E9B-C59471AD00A6}"/>
-    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="55" xr:uid="{3A6C06A0-55B4-49E1-B664-30ED9028E5FB}"/>
+    <cellStyle name="จุลภาค 2" xfId="35" xr:uid="{113598AF-0D37-4EAD-B4DC-91510E1ECBAE}"/>
+    <cellStyle name="ปกติ 10" xfId="36" xr:uid="{9C69A73C-0CA6-4009-88F9-E4215A7BA464}"/>
+    <cellStyle name="ปกติ 11" xfId="37" xr:uid="{00C2975A-3596-49A8-8B4C-EB6AB5FF7D97}"/>
+    <cellStyle name="ปกติ 12" xfId="38" xr:uid="{C39AEE3D-879D-433D-B963-0F02DE6AD3F7}"/>
+    <cellStyle name="ปกติ 13" xfId="39" xr:uid="{258D7836-0DF7-40D9-B657-69D4C18323AF}"/>
+    <cellStyle name="ปกติ 2" xfId="40" xr:uid="{F4FE8401-0175-43BA-A5EC-3FB9FF987F6A}"/>
+    <cellStyle name="ปกติ 2 2" xfId="41" xr:uid="{CCC6DB48-4439-4644-B828-E25CAA873E9E}"/>
+    <cellStyle name="ปกติ 2 3" xfId="42" xr:uid="{A6F23C74-7D22-43FC-8F69-53E3F2EE3AD3}"/>
+    <cellStyle name="ปกติ 2 4" xfId="43" xr:uid="{C98309CC-2EE7-45DA-8964-414136270A64}"/>
+    <cellStyle name="ปกติ 2 5" xfId="44" xr:uid="{6D241921-D698-44DC-9469-B13B95224D33}"/>
+    <cellStyle name="ปกติ 21" xfId="45" xr:uid="{E76E2A77-3FBF-4D09-BE46-D58FA40DF8F4}"/>
+    <cellStyle name="ปกติ 29" xfId="46" xr:uid="{AA140F78-BE2D-4B02-93FA-F9ABC8FC34D5}"/>
+    <cellStyle name="ปกติ 3" xfId="47" xr:uid="{E65F3989-51AF-4248-8929-6CB7145BB018}"/>
+    <cellStyle name="ปกติ 4" xfId="48" xr:uid="{4C525677-ABA0-4FFD-8FDE-8BF5B0F20B61}"/>
+    <cellStyle name="ปกติ 5" xfId="49" xr:uid="{44E64265-B367-497A-8131-BA048205250C}"/>
+    <cellStyle name="ปกติ 6" xfId="50" xr:uid="{CB66BF6A-5B35-4A02-A64C-19FF4ABF4C2D}"/>
+    <cellStyle name="ปกติ 61" xfId="51" xr:uid="{7C930D72-7DF4-4C0D-9DC2-1620AFD70E3E}"/>
+    <cellStyle name="ปกติ 7" xfId="52" xr:uid="{9E4E49D4-4E4F-4178-B727-98C5D928DF0E}"/>
+    <cellStyle name="ปกติ 8" xfId="53" xr:uid="{C37B4265-0A2A-4BE5-B738-BCA4C2E13F1F}"/>
+    <cellStyle name="ปกติ 9" xfId="54" xr:uid="{C844EABA-99E2-4833-9E55-C0181DD0A961}"/>
+    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="55" xr:uid="{8114B1C7-758D-4072-8995-52AB2AA9ED9E}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1425,7 +1425,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7666971-51BA-48B4-A433-BCA4E2619A16}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD072FDC-1D87-4417-BB51-FA26BF5C5603}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -30103,13 +30103,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A19" xr:uid="{0C007589-9EF4-45C6-AB2B-B6653E8E409B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A19" xr:uid="{6BC98581-09B6-404D-82FB-507F554CA173}">
       <formula1>$A$39:$A$43</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{2368FBB0-95EF-43F4-BDDA-03C634C16485}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{FE11A579-4EF2-4DB9-AB95-44E2E8BFDBDF}">
       <formula1>$A$61:$A$73</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J19" xr:uid="{D269A15E-A64C-4F54-8EB2-4AE683489DAC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J19" xr:uid="{FFCB979A-8ACE-4BA8-9980-BF5C54826E8E}">
       <formula1>$A$45:$A$53</formula1>
     </dataValidation>
   </dataValidations>
@@ -30124,7 +30124,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A4732B2-C95C-4DBB-BD57-16689C2ADB16}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81846319-5C13-4DD3-9363-B9113E893C37}">
   <dimension ref="A1:B215"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31004,7 +31004,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABBCF9EB-E268-44C1-9FBB-C1F9588C58AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF7DD2C6-BDE9-4A06-ACC4-CD496DF8DB18}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>

--- a/docs/templates/B5C3-SHORE.xlsx
+++ b/docs/templates/B5C3-SHORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDD2A934-DA82-4788-98FC-7DB2FE11A42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C2187D2-0B40-408B-BBD9-4F04018F9849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{29C08244-6CAE-42EF-8B83-29AF5A6494FC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{808D83F8-9384-4782-8F99-70D45C1D5713}"/>
   </bookViews>
   <sheets>
     <sheet name="DataImport" sheetId="1" r:id="rId1"/>
@@ -1048,62 +1048,62 @@
     </xf>
   </cellXfs>
   <cellStyles count="56">
-    <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{2A61075E-6F51-4970-A69D-296CD5685116}"/>
+    <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{9EAAF9F8-F56F-4318-A7A4-9A12A75B55AB}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="2" xr:uid="{97BEBB86-E161-4B05-8D19-574CBB1278F3}"/>
-    <cellStyle name="Normal 10 10" xfId="3" xr:uid="{050E772B-CC1B-47B6-8252-ACBAEB33A670}"/>
-    <cellStyle name="Normal 10 10 2" xfId="4" xr:uid="{34309A6A-B7F8-498E-AE2A-47A300B97B31}"/>
-    <cellStyle name="Normal 10 2 10" xfId="5" xr:uid="{0ECEABAE-1E2A-4A8C-A631-2ACA4BE6AD35}"/>
-    <cellStyle name="Normal 12" xfId="6" xr:uid="{360AF68B-F1AD-4078-9332-BE8FB73C6327}"/>
-    <cellStyle name="Normal 13" xfId="7" xr:uid="{7D5776B5-A70C-4662-8382-5443107DF926}"/>
-    <cellStyle name="Normal 137" xfId="8" xr:uid="{51198212-6EB1-49E1-9F87-AD3ABE351AEF}"/>
-    <cellStyle name="Normal 14" xfId="9" xr:uid="{69542323-933E-4B2A-8DBD-46E3093BE67C}"/>
-    <cellStyle name="Normal 15" xfId="10" xr:uid="{524D18C0-D358-4123-9BB8-C03B282F8975}"/>
-    <cellStyle name="Normal 2" xfId="11" xr:uid="{5CD0976C-D9A3-48EC-AE07-E44225E9D193}"/>
-    <cellStyle name="Normal 2 10" xfId="12" xr:uid="{4928F55C-926C-448B-B54F-2A58452DDD50}"/>
-    <cellStyle name="Normal 2 10 2" xfId="13" xr:uid="{3F10BAEF-953A-47DF-A051-7C2B303A81F8}"/>
-    <cellStyle name="Normal 2 10 2 2" xfId="14" xr:uid="{90FA1FA6-4A97-425F-8A36-645E53CE5651}"/>
-    <cellStyle name="Normal 2 2" xfId="15" xr:uid="{3DC818D3-517D-481D-821A-3E5AC1A2915E}"/>
-    <cellStyle name="Normal 2 2 10" xfId="16" xr:uid="{C8F13628-D0DD-41F0-90E4-DE3C2FFFDDEF}"/>
-    <cellStyle name="Normal 2 2 2" xfId="17" xr:uid="{6B809E5F-057D-4249-9F44-77D23ABD8A3F}"/>
-    <cellStyle name="Normal 2 2 3" xfId="18" xr:uid="{84CC8274-047A-48EF-8DB8-5BEBAA8341CF}"/>
-    <cellStyle name="Normal 2 3" xfId="19" xr:uid="{C3E60231-0A87-4891-87E0-EAB66D1DFB44}"/>
-    <cellStyle name="Normal 2 4" xfId="20" xr:uid="{6AF4C6E1-07D2-4D1C-8331-08A6437725F9}"/>
-    <cellStyle name="Normal 2 5" xfId="21" xr:uid="{E84D4329-8091-4A08-9A0C-0D1B901971B8}"/>
-    <cellStyle name="Normal 3" xfId="22" xr:uid="{98AC802A-5B69-4FEC-9DCF-88BAD0C28640}"/>
-    <cellStyle name="Normal 3 2" xfId="23" xr:uid="{88154D28-911A-4825-A435-8E2E3746101D}"/>
-    <cellStyle name="Normal 4" xfId="24" xr:uid="{CC01170A-D9DC-45AE-B934-0DF3F22498FA}"/>
-    <cellStyle name="Normal 49" xfId="25" xr:uid="{80EF221E-D9C1-4994-A059-82E15CBF03A1}"/>
-    <cellStyle name="Normal 5" xfId="26" xr:uid="{6EAB46B3-D5CA-4F01-844E-6062034B665C}"/>
-    <cellStyle name="Normal 53" xfId="27" xr:uid="{0790E3D8-4B69-4944-8ECB-AB74C7A25D52}"/>
-    <cellStyle name="Normal 54" xfId="28" xr:uid="{AEA235E2-9A94-4F0E-B959-43A8777EF102}"/>
-    <cellStyle name="Normal 6" xfId="29" xr:uid="{53166880-C3FD-496B-9FA8-95D98AA0A440}"/>
-    <cellStyle name="Normal 7" xfId="30" xr:uid="{90CD75FC-64DD-475B-B957-0BC8DDC477FD}"/>
-    <cellStyle name="Normal 71" xfId="31" xr:uid="{6105A732-DA9D-416D-92AA-F98F73A49A57}"/>
-    <cellStyle name="Normal 8" xfId="32" xr:uid="{445465AA-951A-4568-8D6F-48198A1E5FEC}"/>
-    <cellStyle name="Normal 9" xfId="33" xr:uid="{3DEF6BD9-FB35-4925-BEE3-D4869137AA4C}"/>
+    <cellStyle name="Normal 10" xfId="2" xr:uid="{8741D676-A35B-42DC-9AED-B3FA478676FD}"/>
+    <cellStyle name="Normal 10 10" xfId="3" xr:uid="{190C0ACE-852D-43F8-9C6E-0102448F1742}"/>
+    <cellStyle name="Normal 10 10 2" xfId="4" xr:uid="{924548D0-3F2D-4247-88AE-5A45CA0B7A1F}"/>
+    <cellStyle name="Normal 10 2 10" xfId="5" xr:uid="{79AA0ABD-606E-4655-AFAE-AD9718EC4B14}"/>
+    <cellStyle name="Normal 12" xfId="6" xr:uid="{9DF78826-07D6-44E3-9495-9316757CC84C}"/>
+    <cellStyle name="Normal 13" xfId="7" xr:uid="{88E742FF-F654-498F-AF4C-2EF3B7245210}"/>
+    <cellStyle name="Normal 137" xfId="8" xr:uid="{AC3DE178-155A-4533-8481-96EAB30085B7}"/>
+    <cellStyle name="Normal 14" xfId="9" xr:uid="{7B50137A-7E2B-4835-8226-D4F097CFD703}"/>
+    <cellStyle name="Normal 15" xfId="10" xr:uid="{16AC94EA-8186-41A8-8CAD-62C7F16554E3}"/>
+    <cellStyle name="Normal 2" xfId="11" xr:uid="{6050F885-BA79-4922-B0C2-91418512F8E9}"/>
+    <cellStyle name="Normal 2 10" xfId="12" xr:uid="{E724A116-50E5-4B0B-8BAD-21D54CEC2FCD}"/>
+    <cellStyle name="Normal 2 10 2" xfId="13" xr:uid="{A57AE274-513A-44D4-99AE-1B97356E1B73}"/>
+    <cellStyle name="Normal 2 10 2 2" xfId="14" xr:uid="{3FE0B7D1-F67F-408F-A2E3-CE34F73BF4A7}"/>
+    <cellStyle name="Normal 2 2" xfId="15" xr:uid="{4B8C7B9F-2FDF-4FC3-A170-937CCF992786}"/>
+    <cellStyle name="Normal 2 2 10" xfId="16" xr:uid="{264995EE-74F3-4D68-8181-193500327478}"/>
+    <cellStyle name="Normal 2 2 2" xfId="17" xr:uid="{D4565301-AAB7-477E-887C-4EBFE9433698}"/>
+    <cellStyle name="Normal 2 2 3" xfId="18" xr:uid="{6ABB6F17-2769-471C-A0C4-DC53329FEBC9}"/>
+    <cellStyle name="Normal 2 3" xfId="19" xr:uid="{AB066A4C-7290-4807-A9B1-E0BAA3D4E530}"/>
+    <cellStyle name="Normal 2 4" xfId="20" xr:uid="{E88ED878-191F-4816-B334-9085FC1941E4}"/>
+    <cellStyle name="Normal 2 5" xfId="21" xr:uid="{BF24CB8E-7FE6-45BF-9C7A-4B35D275187F}"/>
+    <cellStyle name="Normal 3" xfId="22" xr:uid="{D3D88E8B-9C4E-4041-AB35-3407EF816563}"/>
+    <cellStyle name="Normal 3 2" xfId="23" xr:uid="{11F96ADD-C361-4BA7-BFAD-81F79B5C3C0B}"/>
+    <cellStyle name="Normal 4" xfId="24" xr:uid="{182C8DF8-C4C6-48A0-A0E9-656ADF6E2A1B}"/>
+    <cellStyle name="Normal 49" xfId="25" xr:uid="{6E62A806-57E8-4BCB-AC4B-A3A1B7EC6F99}"/>
+    <cellStyle name="Normal 5" xfId="26" xr:uid="{214B28FF-2D73-4871-8764-4C5A8674E91E}"/>
+    <cellStyle name="Normal 53" xfId="27" xr:uid="{6DDED5EB-2E42-4A45-8D60-207A73B794F7}"/>
+    <cellStyle name="Normal 54" xfId="28" xr:uid="{96DF212F-BC0F-4567-A0C4-1BB6844E1E20}"/>
+    <cellStyle name="Normal 6" xfId="29" xr:uid="{F16A80D3-D7DD-4D3C-8A22-39E4ADBDEED0}"/>
+    <cellStyle name="Normal 7" xfId="30" xr:uid="{EE06A993-8133-4E10-8E76-2FEA5435F581}"/>
+    <cellStyle name="Normal 71" xfId="31" xr:uid="{CDF0AA3A-A485-41AE-89DB-1BA47D98C64B}"/>
+    <cellStyle name="Normal 8" xfId="32" xr:uid="{E42275E1-1CEA-4E06-ABE1-F61785575633}"/>
+    <cellStyle name="Normal 9" xfId="33" xr:uid="{24E65991-1B2E-4A00-936B-26E9C1D3D62F}"/>
     <cellStyle name="Percent" xfId="34" builtinId="5"/>
-    <cellStyle name="จุลภาค 2" xfId="35" xr:uid="{113598AF-0D37-4EAD-B4DC-91510E1ECBAE}"/>
-    <cellStyle name="ปกติ 10" xfId="36" xr:uid="{9C69A73C-0CA6-4009-88F9-E4215A7BA464}"/>
-    <cellStyle name="ปกติ 11" xfId="37" xr:uid="{00C2975A-3596-49A8-8B4C-EB6AB5FF7D97}"/>
-    <cellStyle name="ปกติ 12" xfId="38" xr:uid="{C39AEE3D-879D-433D-B963-0F02DE6AD3F7}"/>
-    <cellStyle name="ปกติ 13" xfId="39" xr:uid="{258D7836-0DF7-40D9-B657-69D4C18323AF}"/>
-    <cellStyle name="ปกติ 2" xfId="40" xr:uid="{F4FE8401-0175-43BA-A5EC-3FB9FF987F6A}"/>
-    <cellStyle name="ปกติ 2 2" xfId="41" xr:uid="{CCC6DB48-4439-4644-B828-E25CAA873E9E}"/>
-    <cellStyle name="ปกติ 2 3" xfId="42" xr:uid="{A6F23C74-7D22-43FC-8F69-53E3F2EE3AD3}"/>
-    <cellStyle name="ปกติ 2 4" xfId="43" xr:uid="{C98309CC-2EE7-45DA-8964-414136270A64}"/>
-    <cellStyle name="ปกติ 2 5" xfId="44" xr:uid="{6D241921-D698-44DC-9469-B13B95224D33}"/>
-    <cellStyle name="ปกติ 21" xfId="45" xr:uid="{E76E2A77-3FBF-4D09-BE46-D58FA40DF8F4}"/>
-    <cellStyle name="ปกติ 29" xfId="46" xr:uid="{AA140F78-BE2D-4B02-93FA-F9ABC8FC34D5}"/>
-    <cellStyle name="ปกติ 3" xfId="47" xr:uid="{E65F3989-51AF-4248-8929-6CB7145BB018}"/>
-    <cellStyle name="ปกติ 4" xfId="48" xr:uid="{4C525677-ABA0-4FFD-8FDE-8BF5B0F20B61}"/>
-    <cellStyle name="ปกติ 5" xfId="49" xr:uid="{44E64265-B367-497A-8131-BA048205250C}"/>
-    <cellStyle name="ปกติ 6" xfId="50" xr:uid="{CB66BF6A-5B35-4A02-A64C-19FF4ABF4C2D}"/>
-    <cellStyle name="ปกติ 61" xfId="51" xr:uid="{7C930D72-7DF4-4C0D-9DC2-1620AFD70E3E}"/>
-    <cellStyle name="ปกติ 7" xfId="52" xr:uid="{9E4E49D4-4E4F-4178-B727-98C5D928DF0E}"/>
-    <cellStyle name="ปกติ 8" xfId="53" xr:uid="{C37B4265-0A2A-4BE5-B738-BCA4C2E13F1F}"/>
-    <cellStyle name="ปกติ 9" xfId="54" xr:uid="{C844EABA-99E2-4833-9E55-C0181DD0A961}"/>
-    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="55" xr:uid="{8114B1C7-758D-4072-8995-52AB2AA9ED9E}"/>
+    <cellStyle name="จุลภาค 2" xfId="35" xr:uid="{2FC32705-A314-479F-95D4-BCD18A3AE0AA}"/>
+    <cellStyle name="ปกติ 10" xfId="36" xr:uid="{00CCD9A6-65CD-4B96-8103-1BBE26B55826}"/>
+    <cellStyle name="ปกติ 11" xfId="37" xr:uid="{FDD85256-ED94-4B1E-91BB-477271B55CF2}"/>
+    <cellStyle name="ปกติ 12" xfId="38" xr:uid="{464B7687-C9F8-4E2F-93E6-DDF53F6A3A78}"/>
+    <cellStyle name="ปกติ 13" xfId="39" xr:uid="{38D660CF-AC19-46D9-A61F-3A01C67A97F0}"/>
+    <cellStyle name="ปกติ 2" xfId="40" xr:uid="{8422684F-7A09-4274-A1CD-89B1385EA8A0}"/>
+    <cellStyle name="ปกติ 2 2" xfId="41" xr:uid="{BBBC827D-A500-46DC-93C9-2A275B425AAD}"/>
+    <cellStyle name="ปกติ 2 3" xfId="42" xr:uid="{EA9FD8D1-E7EA-4A9C-9A69-E61464F6DE6E}"/>
+    <cellStyle name="ปกติ 2 4" xfId="43" xr:uid="{ACDC6EC1-8559-43EE-A296-DC9224A3A9BA}"/>
+    <cellStyle name="ปกติ 2 5" xfId="44" xr:uid="{AC03393D-21E9-4011-93BB-729395ED1C9E}"/>
+    <cellStyle name="ปกติ 21" xfId="45" xr:uid="{564E7F97-DB15-4B15-991F-7007285B1446}"/>
+    <cellStyle name="ปกติ 29" xfId="46" xr:uid="{A1329EE8-D088-476A-9B60-E5CC39D7B750}"/>
+    <cellStyle name="ปกติ 3" xfId="47" xr:uid="{C226624D-90B6-4763-B392-B217FD281063}"/>
+    <cellStyle name="ปกติ 4" xfId="48" xr:uid="{8E6AAC9F-0460-4864-B5AB-44C6ECBE391D}"/>
+    <cellStyle name="ปกติ 5" xfId="49" xr:uid="{C66101EE-35B6-43A4-98FF-2D8E1692BF71}"/>
+    <cellStyle name="ปกติ 6" xfId="50" xr:uid="{5C9F8768-70D0-4FA4-B757-C836185C1B8D}"/>
+    <cellStyle name="ปกติ 61" xfId="51" xr:uid="{F5B95E0D-E786-4636-855B-A19EA9ADEC02}"/>
+    <cellStyle name="ปกติ 7" xfId="52" xr:uid="{5872C70D-17E6-42B2-882D-DD84BBBD3F85}"/>
+    <cellStyle name="ปกติ 8" xfId="53" xr:uid="{59E4BBFB-7482-4441-A571-A144FAC8CC84}"/>
+    <cellStyle name="ปกติ 9" xfId="54" xr:uid="{50F41DFB-934F-4850-B597-258B2C63AAC6}"/>
+    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="55" xr:uid="{AA12C34E-5069-4E9F-B4B6-3254049CA977}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1425,7 +1425,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD072FDC-1D87-4417-BB51-FA26BF5C5603}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A9965A-34DA-46D6-8540-399F56F40F43}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -30103,13 +30103,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A19" xr:uid="{6BC98581-09B6-404D-82FB-507F554CA173}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A19" xr:uid="{594B9FD8-B28D-425F-BBF5-F914FE89DF39}">
       <formula1>$A$39:$A$43</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{FE11A579-4EF2-4DB9-AB95-44E2E8BFDBDF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{EDF06B07-4F4E-4EB6-833D-113F0943A724}">
       <formula1>$A$61:$A$73</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J19" xr:uid="{FFCB979A-8ACE-4BA8-9980-BF5C54826E8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J19" xr:uid="{86C3936C-4263-40AC-A65D-220A0DA0CC52}">
       <formula1>$A$45:$A$53</formula1>
     </dataValidation>
   </dataValidations>
@@ -30124,7 +30124,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81846319-5C13-4DD3-9363-B9113E893C37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{495800B9-697F-4D5A-A94C-BE2E1AC21685}">
   <dimension ref="A1:B215"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31004,7 +31004,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF7DD2C6-BDE9-4A06-ACC4-CD496DF8DB18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958EDCFD-0609-4E6F-A55D-463F8C4300F9}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>

--- a/docs/templates/B5C3-SHORE.xlsx
+++ b/docs/templates/B5C3-SHORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C2187D2-0B40-408B-BBD9-4F04018F9849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCD8D122-3A95-40BB-8985-7EEFA6CADC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{808D83F8-9384-4782-8F99-70D45C1D5713}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D3C618F3-B36E-4196-AD10-4468B6182EFC}"/>
   </bookViews>
   <sheets>
     <sheet name="DataImport" sheetId="1" r:id="rId1"/>
@@ -1048,62 +1048,62 @@
     </xf>
   </cellXfs>
   <cellStyles count="56">
-    <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{9EAAF9F8-F56F-4318-A7A4-9A12A75B55AB}"/>
+    <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{F297820C-37E8-450C-9A41-DE1816E26D8B}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="2" xr:uid="{8741D676-A35B-42DC-9AED-B3FA478676FD}"/>
-    <cellStyle name="Normal 10 10" xfId="3" xr:uid="{190C0ACE-852D-43F8-9C6E-0102448F1742}"/>
-    <cellStyle name="Normal 10 10 2" xfId="4" xr:uid="{924548D0-3F2D-4247-88AE-5A45CA0B7A1F}"/>
-    <cellStyle name="Normal 10 2 10" xfId="5" xr:uid="{79AA0ABD-606E-4655-AFAE-AD9718EC4B14}"/>
-    <cellStyle name="Normal 12" xfId="6" xr:uid="{9DF78826-07D6-44E3-9495-9316757CC84C}"/>
-    <cellStyle name="Normal 13" xfId="7" xr:uid="{88E742FF-F654-498F-AF4C-2EF3B7245210}"/>
-    <cellStyle name="Normal 137" xfId="8" xr:uid="{AC3DE178-155A-4533-8481-96EAB30085B7}"/>
-    <cellStyle name="Normal 14" xfId="9" xr:uid="{7B50137A-7E2B-4835-8226-D4F097CFD703}"/>
-    <cellStyle name="Normal 15" xfId="10" xr:uid="{16AC94EA-8186-41A8-8CAD-62C7F16554E3}"/>
-    <cellStyle name="Normal 2" xfId="11" xr:uid="{6050F885-BA79-4922-B0C2-91418512F8E9}"/>
-    <cellStyle name="Normal 2 10" xfId="12" xr:uid="{E724A116-50E5-4B0B-8BAD-21D54CEC2FCD}"/>
-    <cellStyle name="Normal 2 10 2" xfId="13" xr:uid="{A57AE274-513A-44D4-99AE-1B97356E1B73}"/>
-    <cellStyle name="Normal 2 10 2 2" xfId="14" xr:uid="{3FE0B7D1-F67F-408F-A2E3-CE34F73BF4A7}"/>
-    <cellStyle name="Normal 2 2" xfId="15" xr:uid="{4B8C7B9F-2FDF-4FC3-A170-937CCF992786}"/>
-    <cellStyle name="Normal 2 2 10" xfId="16" xr:uid="{264995EE-74F3-4D68-8181-193500327478}"/>
-    <cellStyle name="Normal 2 2 2" xfId="17" xr:uid="{D4565301-AAB7-477E-887C-4EBFE9433698}"/>
-    <cellStyle name="Normal 2 2 3" xfId="18" xr:uid="{6ABB6F17-2769-471C-A0C4-DC53329FEBC9}"/>
-    <cellStyle name="Normal 2 3" xfId="19" xr:uid="{AB066A4C-7290-4807-A9B1-E0BAA3D4E530}"/>
-    <cellStyle name="Normal 2 4" xfId="20" xr:uid="{E88ED878-191F-4816-B334-9085FC1941E4}"/>
-    <cellStyle name="Normal 2 5" xfId="21" xr:uid="{BF24CB8E-7FE6-45BF-9C7A-4B35D275187F}"/>
-    <cellStyle name="Normal 3" xfId="22" xr:uid="{D3D88E8B-9C4E-4041-AB35-3407EF816563}"/>
-    <cellStyle name="Normal 3 2" xfId="23" xr:uid="{11F96ADD-C361-4BA7-BFAD-81F79B5C3C0B}"/>
-    <cellStyle name="Normal 4" xfId="24" xr:uid="{182C8DF8-C4C6-48A0-A0E9-656ADF6E2A1B}"/>
-    <cellStyle name="Normal 49" xfId="25" xr:uid="{6E62A806-57E8-4BCB-AC4B-A3A1B7EC6F99}"/>
-    <cellStyle name="Normal 5" xfId="26" xr:uid="{214B28FF-2D73-4871-8764-4C5A8674E91E}"/>
-    <cellStyle name="Normal 53" xfId="27" xr:uid="{6DDED5EB-2E42-4A45-8D60-207A73B794F7}"/>
-    <cellStyle name="Normal 54" xfId="28" xr:uid="{96DF212F-BC0F-4567-A0C4-1BB6844E1E20}"/>
-    <cellStyle name="Normal 6" xfId="29" xr:uid="{F16A80D3-D7DD-4D3C-8A22-39E4ADBDEED0}"/>
-    <cellStyle name="Normal 7" xfId="30" xr:uid="{EE06A993-8133-4E10-8E76-2FEA5435F581}"/>
-    <cellStyle name="Normal 71" xfId="31" xr:uid="{CDF0AA3A-A485-41AE-89DB-1BA47D98C64B}"/>
-    <cellStyle name="Normal 8" xfId="32" xr:uid="{E42275E1-1CEA-4E06-ABE1-F61785575633}"/>
-    <cellStyle name="Normal 9" xfId="33" xr:uid="{24E65991-1B2E-4A00-936B-26E9C1D3D62F}"/>
+    <cellStyle name="Normal 10" xfId="2" xr:uid="{7547E959-B0DD-4D32-A4A6-1D3F9201A2D1}"/>
+    <cellStyle name="Normal 10 10" xfId="3" xr:uid="{3F5346C3-7CD7-4F43-9BA9-B108AA41EA5D}"/>
+    <cellStyle name="Normal 10 10 2" xfId="4" xr:uid="{F22A6C74-3A61-46E1-8680-00A7D23D8EB4}"/>
+    <cellStyle name="Normal 10 2 10" xfId="5" xr:uid="{538DF196-D7E7-4F11-B061-6D0DD7E3232C}"/>
+    <cellStyle name="Normal 12" xfId="6" xr:uid="{071A83C2-1E42-4ED9-A127-C2F596A3776F}"/>
+    <cellStyle name="Normal 13" xfId="7" xr:uid="{0A492D8E-D7D6-473D-A7B4-4D4C105A1ABE}"/>
+    <cellStyle name="Normal 137" xfId="8" xr:uid="{063B116A-79AE-44A1-997E-29CA68B2AD38}"/>
+    <cellStyle name="Normal 14" xfId="9" xr:uid="{B7B2E9A6-3B9C-4DC4-A4C3-B04F922DEF98}"/>
+    <cellStyle name="Normal 15" xfId="10" xr:uid="{956C9346-A80F-4EC6-98B1-EE3BEDCF5B1D}"/>
+    <cellStyle name="Normal 2" xfId="11" xr:uid="{62B748E1-9CBD-4BEE-B2B4-4DE5F0BBF966}"/>
+    <cellStyle name="Normal 2 10" xfId="12" xr:uid="{10572207-B22E-4ED4-B40C-6A1E373543A9}"/>
+    <cellStyle name="Normal 2 10 2" xfId="13" xr:uid="{2CE5328A-3061-4129-8CB9-60BFAD80A88E}"/>
+    <cellStyle name="Normal 2 10 2 2" xfId="14" xr:uid="{7C44E203-2CAC-4403-89D7-F42E3D46BEB5}"/>
+    <cellStyle name="Normal 2 2" xfId="15" xr:uid="{22C75738-6563-40CE-AC59-69ABA25543B2}"/>
+    <cellStyle name="Normal 2 2 10" xfId="16" xr:uid="{10ACE165-D655-48B2-A9DB-0AF1DBB53755}"/>
+    <cellStyle name="Normal 2 2 2" xfId="17" xr:uid="{5C4C92C9-696A-4F62-BA3E-FD3AB994E002}"/>
+    <cellStyle name="Normal 2 2 3" xfId="18" xr:uid="{8BB46C94-A540-4C8B-AE98-3B9F45CC8487}"/>
+    <cellStyle name="Normal 2 3" xfId="19" xr:uid="{3DDF6B79-E7D5-420A-9F2C-F9545973B4E8}"/>
+    <cellStyle name="Normal 2 4" xfId="20" xr:uid="{04CCD166-4C78-4FDB-8EC5-1441B1405A2C}"/>
+    <cellStyle name="Normal 2 5" xfId="21" xr:uid="{3035B3BA-80C1-455A-B3E8-7C70F6D8AFF8}"/>
+    <cellStyle name="Normal 3" xfId="22" xr:uid="{0BCE0207-C62E-4B59-9AAA-3CAAEF8EAB76}"/>
+    <cellStyle name="Normal 3 2" xfId="23" xr:uid="{4527F518-2A22-4867-9DB0-0AA543342413}"/>
+    <cellStyle name="Normal 4" xfId="24" xr:uid="{5D80B49E-971A-4F70-A35C-0C0A986B4F2D}"/>
+    <cellStyle name="Normal 49" xfId="25" xr:uid="{0F1B68A6-0856-453F-8D91-050D984B269D}"/>
+    <cellStyle name="Normal 5" xfId="26" xr:uid="{D03385F0-E118-4B6C-9E0F-E4A6C8CEEB60}"/>
+    <cellStyle name="Normal 53" xfId="27" xr:uid="{9D2A2F21-6954-49CC-9E3F-0B4B43D2D628}"/>
+    <cellStyle name="Normal 54" xfId="28" xr:uid="{A4E3EC56-F829-4E00-8FCE-41D23E26B66F}"/>
+    <cellStyle name="Normal 6" xfId="29" xr:uid="{BCB85DDD-462C-4D65-8836-89A361D74D20}"/>
+    <cellStyle name="Normal 7" xfId="30" xr:uid="{5814953F-831F-4169-B6FC-B2B061F5677A}"/>
+    <cellStyle name="Normal 71" xfId="31" xr:uid="{7522D2BC-15BA-4B56-96EF-8C266A2A08F2}"/>
+    <cellStyle name="Normal 8" xfId="32" xr:uid="{648E3E8F-BA8E-4B71-8079-5E11F2BFD932}"/>
+    <cellStyle name="Normal 9" xfId="33" xr:uid="{15302FA0-6C41-4EB0-A88E-B0F616805788}"/>
     <cellStyle name="Percent" xfId="34" builtinId="5"/>
-    <cellStyle name="จุลภาค 2" xfId="35" xr:uid="{2FC32705-A314-479F-95D4-BCD18A3AE0AA}"/>
-    <cellStyle name="ปกติ 10" xfId="36" xr:uid="{00CCD9A6-65CD-4B96-8103-1BBE26B55826}"/>
-    <cellStyle name="ปกติ 11" xfId="37" xr:uid="{FDD85256-ED94-4B1E-91BB-477271B55CF2}"/>
-    <cellStyle name="ปกติ 12" xfId="38" xr:uid="{464B7687-C9F8-4E2F-93E6-DDF53F6A3A78}"/>
-    <cellStyle name="ปกติ 13" xfId="39" xr:uid="{38D660CF-AC19-46D9-A61F-3A01C67A97F0}"/>
-    <cellStyle name="ปกติ 2" xfId="40" xr:uid="{8422684F-7A09-4274-A1CD-89B1385EA8A0}"/>
-    <cellStyle name="ปกติ 2 2" xfId="41" xr:uid="{BBBC827D-A500-46DC-93C9-2A275B425AAD}"/>
-    <cellStyle name="ปกติ 2 3" xfId="42" xr:uid="{EA9FD8D1-E7EA-4A9C-9A69-E61464F6DE6E}"/>
-    <cellStyle name="ปกติ 2 4" xfId="43" xr:uid="{ACDC6EC1-8559-43EE-A296-DC9224A3A9BA}"/>
-    <cellStyle name="ปกติ 2 5" xfId="44" xr:uid="{AC03393D-21E9-4011-93BB-729395ED1C9E}"/>
-    <cellStyle name="ปกติ 21" xfId="45" xr:uid="{564E7F97-DB15-4B15-991F-7007285B1446}"/>
-    <cellStyle name="ปกติ 29" xfId="46" xr:uid="{A1329EE8-D088-476A-9B60-E5CC39D7B750}"/>
-    <cellStyle name="ปกติ 3" xfId="47" xr:uid="{C226624D-90B6-4763-B392-B217FD281063}"/>
-    <cellStyle name="ปกติ 4" xfId="48" xr:uid="{8E6AAC9F-0460-4864-B5AB-44C6ECBE391D}"/>
-    <cellStyle name="ปกติ 5" xfId="49" xr:uid="{C66101EE-35B6-43A4-98FF-2D8E1692BF71}"/>
-    <cellStyle name="ปกติ 6" xfId="50" xr:uid="{5C9F8768-70D0-4FA4-B757-C836185C1B8D}"/>
-    <cellStyle name="ปกติ 61" xfId="51" xr:uid="{F5B95E0D-E786-4636-855B-A19EA9ADEC02}"/>
-    <cellStyle name="ปกติ 7" xfId="52" xr:uid="{5872C70D-17E6-42B2-882D-DD84BBBD3F85}"/>
-    <cellStyle name="ปกติ 8" xfId="53" xr:uid="{59E4BBFB-7482-4441-A571-A144FAC8CC84}"/>
-    <cellStyle name="ปกติ 9" xfId="54" xr:uid="{50F41DFB-934F-4850-B597-258B2C63AAC6}"/>
-    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="55" xr:uid="{AA12C34E-5069-4E9F-B4B6-3254049CA977}"/>
+    <cellStyle name="จุลภาค 2" xfId="35" xr:uid="{E955AD5A-4160-45F0-B725-23CDBB33197F}"/>
+    <cellStyle name="ปกติ 10" xfId="36" xr:uid="{E2EF45A5-BA91-47B5-BC31-C44816D90562}"/>
+    <cellStyle name="ปกติ 11" xfId="37" xr:uid="{7AC01BED-244F-4C6E-AC81-D7BC69D96E66}"/>
+    <cellStyle name="ปกติ 12" xfId="38" xr:uid="{8CFEEE67-2F72-428C-B489-CD23F8C91842}"/>
+    <cellStyle name="ปกติ 13" xfId="39" xr:uid="{833C3268-EBA3-4398-BD61-D25FD82C4A0C}"/>
+    <cellStyle name="ปกติ 2" xfId="40" xr:uid="{D979F4CA-0321-427E-AC1D-CB9A338B123F}"/>
+    <cellStyle name="ปกติ 2 2" xfId="41" xr:uid="{FE1A5496-3D6F-4146-B133-DDEE9144AE5F}"/>
+    <cellStyle name="ปกติ 2 3" xfId="42" xr:uid="{A98818BF-FCAC-4541-AFC7-FFE42F2E4530}"/>
+    <cellStyle name="ปกติ 2 4" xfId="43" xr:uid="{9345FF16-FD41-4225-9C4E-BABD17828631}"/>
+    <cellStyle name="ปกติ 2 5" xfId="44" xr:uid="{63F41DCD-175A-4DDA-845B-D6FF4C7F62A0}"/>
+    <cellStyle name="ปกติ 21" xfId="45" xr:uid="{0330616E-B6A5-4A61-BD91-C382D31A8F35}"/>
+    <cellStyle name="ปกติ 29" xfId="46" xr:uid="{C75FC74F-F168-4F11-8BA9-FF31BEE52D35}"/>
+    <cellStyle name="ปกติ 3" xfId="47" xr:uid="{92FA2506-6B39-4DA9-876D-F17B0D4137A8}"/>
+    <cellStyle name="ปกติ 4" xfId="48" xr:uid="{44E35319-1B00-41F8-B18D-BC1065306684}"/>
+    <cellStyle name="ปกติ 5" xfId="49" xr:uid="{C3A6966D-D64E-4203-AC30-E891D02E6B68}"/>
+    <cellStyle name="ปกติ 6" xfId="50" xr:uid="{4474BEEB-8848-4E86-9E7D-1B4F84CCEEAE}"/>
+    <cellStyle name="ปกติ 61" xfId="51" xr:uid="{B7B6DFAA-A37A-4478-9270-6862AF381BDA}"/>
+    <cellStyle name="ปกติ 7" xfId="52" xr:uid="{8096B27C-BAD6-43A2-8D13-CFB0A69B7FC4}"/>
+    <cellStyle name="ปกติ 8" xfId="53" xr:uid="{65794A03-C2FA-4BD5-B6BA-5885EA6A5D20}"/>
+    <cellStyle name="ปกติ 9" xfId="54" xr:uid="{5453A0F4-4F25-40E8-9961-43EBD0737343}"/>
+    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="55" xr:uid="{F70D1C98-1B08-4F93-B96B-3535C35F467C}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1425,7 +1425,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A9965A-34DA-46D6-8540-399F56F40F43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0A59DFF-C30E-4D9A-968A-6148763A845A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -30103,13 +30103,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A19" xr:uid="{594B9FD8-B28D-425F-BBF5-F914FE89DF39}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A19" xr:uid="{E699E016-504B-4D32-AB7E-93B5C3704A85}">
       <formula1>$A$39:$A$43</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{EDF06B07-4F4E-4EB6-833D-113F0943A724}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{36BD2DA1-30D3-45E4-A0BB-5CEBBCDFA32B}">
       <formula1>$A$61:$A$73</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J19" xr:uid="{86C3936C-4263-40AC-A65D-220A0DA0CC52}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J19" xr:uid="{57A3A4EE-9715-4864-8E22-7C83BEE3400F}">
       <formula1>$A$45:$A$53</formula1>
     </dataValidation>
   </dataValidations>
@@ -30124,7 +30124,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{495800B9-697F-4D5A-A94C-BE2E1AC21685}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17C2A883-2960-47CE-8C31-194136E4E65E}">
   <dimension ref="A1:B215"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31004,7 +31004,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958EDCFD-0609-4E6F-A55D-463F8C4300F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B757ADAF-19E1-4CC6-8E2F-7795AA830A30}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>

--- a/docs/templates/B5C3-SHORE.xlsx
+++ b/docs/templates/B5C3-SHORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53CC725D-82A5-4D7A-8418-0564F56C84A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B9FFA4E-8C31-46B6-A96D-51729A14C82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="1440" windowWidth="21600" windowHeight="11235" xr2:uid="{C6AF8611-A13E-4D9C-B1FD-654D95D91C39}"/>
+    <workbookView xWindow="30675" yWindow="1875" windowWidth="21600" windowHeight="11235" xr2:uid="{5CFA91C8-C6C0-445E-9926-EFD0BC8BAAB9}"/>
   </bookViews>
   <sheets>
     <sheet name="DataImport" sheetId="1" r:id="rId1"/>
@@ -1086,62 +1086,62 @@
     </xf>
   </cellXfs>
   <cellStyles count="56">
-    <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{B2254A43-90FE-4393-AE02-E43C5A6BF455}"/>
+    <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{74FC0B57-3591-4006-85B9-B625F5CB8AC5}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="2" xr:uid="{268B7566-53BC-46ED-A645-3124E28C31B0}"/>
-    <cellStyle name="Normal 10 10" xfId="3" xr:uid="{F1B3344A-EAF9-4E3F-B636-CE0DB38A09F6}"/>
-    <cellStyle name="Normal 10 10 2" xfId="4" xr:uid="{E10593A1-7E94-4117-AEC0-2879142A64E7}"/>
-    <cellStyle name="Normal 10 2 10" xfId="5" xr:uid="{F5631E55-EF84-4A38-9601-2E7CA20A91BE}"/>
-    <cellStyle name="Normal 12" xfId="6" xr:uid="{049DDC00-65D4-44B4-9DC6-F2E857DC5998}"/>
-    <cellStyle name="Normal 13" xfId="7" xr:uid="{526E699E-0EA4-4825-8BB8-586081797CEA}"/>
-    <cellStyle name="Normal 137" xfId="8" xr:uid="{0B86B7F6-75A5-435A-8F2F-EB204B8EEFC8}"/>
-    <cellStyle name="Normal 14" xfId="9" xr:uid="{F6D111E1-0E64-4F84-8A92-24D0FBB259F3}"/>
-    <cellStyle name="Normal 15" xfId="10" xr:uid="{A242FFB2-7BB4-4128-88F4-FA7DA12EFB13}"/>
-    <cellStyle name="Normal 2" xfId="11" xr:uid="{48C6874A-606E-4F79-9A2B-B7318CAF5D22}"/>
-    <cellStyle name="Normal 2 10" xfId="12" xr:uid="{C268AD9A-F66A-4602-BD1A-272495DD4BF2}"/>
-    <cellStyle name="Normal 2 10 2" xfId="13" xr:uid="{8BA0250A-DBAC-45E1-AC08-9A71506B7381}"/>
-    <cellStyle name="Normal 2 10 2 2" xfId="14" xr:uid="{64062A0C-9102-419E-BF5F-FF8922974F97}"/>
-    <cellStyle name="Normal 2 2" xfId="15" xr:uid="{32120D43-A053-41F1-BEF9-39CCAB834B49}"/>
-    <cellStyle name="Normal 2 2 10" xfId="16" xr:uid="{7447ADA6-DCDC-49DA-9DD5-B13DB99FFA9D}"/>
-    <cellStyle name="Normal 2 2 2" xfId="17" xr:uid="{BD2340C7-AA51-4A22-BBEC-851C0793ABD4}"/>
-    <cellStyle name="Normal 2 2 3" xfId="18" xr:uid="{DE705EC7-3F69-492D-801B-2C766628D82C}"/>
-    <cellStyle name="Normal 2 3" xfId="19" xr:uid="{F4355663-8780-476F-A99A-3575F8318A2B}"/>
-    <cellStyle name="Normal 2 4" xfId="20" xr:uid="{4B883F85-569A-45F7-8D53-BFDB499A3EB9}"/>
-    <cellStyle name="Normal 2 5" xfId="21" xr:uid="{E84B5EC7-1D7E-4DA4-B15E-4A2D5C315350}"/>
-    <cellStyle name="Normal 3" xfId="22" xr:uid="{74A409EC-3989-4E06-9880-24E8905892D3}"/>
-    <cellStyle name="Normal 3 2" xfId="23" xr:uid="{DB1F7D68-C7E6-4FCE-B7FD-5E245900B06F}"/>
-    <cellStyle name="Normal 4" xfId="24" xr:uid="{D822510E-725D-42E1-9A85-B86186568015}"/>
-    <cellStyle name="Normal 49" xfId="25" xr:uid="{ABEAD76C-F2DC-4826-9C9A-492C5378C07E}"/>
-    <cellStyle name="Normal 5" xfId="26" xr:uid="{1F7730B3-9F51-43A3-94E3-ABD5048181AF}"/>
-    <cellStyle name="Normal 53" xfId="27" xr:uid="{D7777521-5918-4C29-BBCE-6D3F5A2BAC7F}"/>
-    <cellStyle name="Normal 54" xfId="28" xr:uid="{4F81715C-B272-4B27-B654-484BAAE659D4}"/>
-    <cellStyle name="Normal 6" xfId="29" xr:uid="{AA3B779E-D217-464A-BC85-C0CD7FC04C94}"/>
-    <cellStyle name="Normal 7" xfId="30" xr:uid="{84239B45-D31C-411A-BCDC-0E6BDCA08837}"/>
-    <cellStyle name="Normal 71" xfId="31" xr:uid="{B318C7D1-42CE-4942-B63B-D6299AD45E1F}"/>
-    <cellStyle name="Normal 8" xfId="32" xr:uid="{A7737CB4-DACB-409C-AAF7-7E03E778CCB7}"/>
-    <cellStyle name="Normal 9" xfId="33" xr:uid="{04142AD5-7D0E-40F7-98A8-D7D159141532}"/>
+    <cellStyle name="Normal 10" xfId="2" xr:uid="{3BF8FB53-3568-425C-8A39-EC3C6463BAB1}"/>
+    <cellStyle name="Normal 10 10" xfId="3" xr:uid="{40D939EE-78A7-49E7-9564-7C8E5B5558E1}"/>
+    <cellStyle name="Normal 10 10 2" xfId="4" xr:uid="{82556806-6427-48BE-8720-1F49A32BCDBA}"/>
+    <cellStyle name="Normal 10 2 10" xfId="5" xr:uid="{C36EE43A-938E-450B-8CAA-210147F14DD5}"/>
+    <cellStyle name="Normal 12" xfId="6" xr:uid="{5F019719-602B-4126-83D7-A84FF70E9F3F}"/>
+    <cellStyle name="Normal 13" xfId="7" xr:uid="{5EB05BD8-2311-48E8-B413-22CE9CD920DE}"/>
+    <cellStyle name="Normal 137" xfId="8" xr:uid="{BBED5B8B-60F5-4366-93A9-DD53966D1D64}"/>
+    <cellStyle name="Normal 14" xfId="9" xr:uid="{707ECBD6-5CDD-4D12-A872-20529EA3700F}"/>
+    <cellStyle name="Normal 15" xfId="10" xr:uid="{29E043AE-6CB0-4AFA-9E72-E76C99F9ADDD}"/>
+    <cellStyle name="Normal 2" xfId="11" xr:uid="{BD21FA43-E3F7-46D0-B63F-63ABC64321ED}"/>
+    <cellStyle name="Normal 2 10" xfId="12" xr:uid="{E34505AB-C34A-44BD-A206-577F9C1DA27B}"/>
+    <cellStyle name="Normal 2 10 2" xfId="13" xr:uid="{A7E2EA10-3830-4A6E-970E-ACA20C3F7F52}"/>
+    <cellStyle name="Normal 2 10 2 2" xfId="14" xr:uid="{720EFF66-5B17-45A5-8921-7E3750CE1162}"/>
+    <cellStyle name="Normal 2 2" xfId="15" xr:uid="{9A073E21-B5D1-469C-B072-BE178C4A4DEF}"/>
+    <cellStyle name="Normal 2 2 10" xfId="16" xr:uid="{80733780-37D9-4FAE-9BA7-7D581F194BD7}"/>
+    <cellStyle name="Normal 2 2 2" xfId="17" xr:uid="{4FD8A771-9C85-45A5-8A36-0C6E92AAB442}"/>
+    <cellStyle name="Normal 2 2 3" xfId="18" xr:uid="{748EB0D9-E1BC-4808-8D5A-31C28823544A}"/>
+    <cellStyle name="Normal 2 3" xfId="19" xr:uid="{D0DE7B39-338D-4C4B-8B78-6D429612BAEE}"/>
+    <cellStyle name="Normal 2 4" xfId="20" xr:uid="{06B1819A-8DDE-4CA4-9700-EDA71C3205F4}"/>
+    <cellStyle name="Normal 2 5" xfId="21" xr:uid="{D6DB176D-E49D-4678-90A0-14AA7B74B928}"/>
+    <cellStyle name="Normal 3" xfId="22" xr:uid="{3ECFB382-2099-43B5-ABA1-11E4E52D8840}"/>
+    <cellStyle name="Normal 3 2" xfId="23" xr:uid="{112922E3-DA5D-4CB6-9571-D9BEF2493396}"/>
+    <cellStyle name="Normal 4" xfId="24" xr:uid="{9C69C58C-1C94-41AF-B85F-F7EF8E3593CC}"/>
+    <cellStyle name="Normal 49" xfId="25" xr:uid="{7ACFE984-C248-4EDD-9783-DF1A7593B0FC}"/>
+    <cellStyle name="Normal 5" xfId="26" xr:uid="{E9FFE19D-BD8B-461B-BB0E-3CEA07527461}"/>
+    <cellStyle name="Normal 53" xfId="27" xr:uid="{468F4DFF-0E5C-4D01-B0D0-761DA6AF7F9D}"/>
+    <cellStyle name="Normal 54" xfId="28" xr:uid="{F3362774-577F-4632-82CC-FD42B6F220CE}"/>
+    <cellStyle name="Normal 6" xfId="29" xr:uid="{FA92F8A3-9318-44B7-9AA3-8B7ECD631B4D}"/>
+    <cellStyle name="Normal 7" xfId="30" xr:uid="{9309347C-B59C-4A64-ABC1-B4A7F30EEF85}"/>
+    <cellStyle name="Normal 71" xfId="31" xr:uid="{EAFEFFB7-FADE-4744-8AA2-AE15BB2373C3}"/>
+    <cellStyle name="Normal 8" xfId="32" xr:uid="{E954AF63-C499-43A9-A1F8-7A0157D807AD}"/>
+    <cellStyle name="Normal 9" xfId="33" xr:uid="{B1CF1C72-F5B1-4E02-B446-0773B74A5FC2}"/>
     <cellStyle name="Percent" xfId="34" builtinId="5"/>
-    <cellStyle name="จุลภาค 2" xfId="35" xr:uid="{65CC808E-3ED6-4C6B-8B7F-E71A12E31B79}"/>
-    <cellStyle name="ปกติ 10" xfId="36" xr:uid="{3FBAB6DE-38F2-47B7-8766-74E665BCC3A8}"/>
-    <cellStyle name="ปกติ 11" xfId="37" xr:uid="{1BC38AD6-70AE-4CFA-B193-08F4B6E01DB4}"/>
-    <cellStyle name="ปกติ 12" xfId="38" xr:uid="{90980966-99A9-42EF-9E22-D4A60093567A}"/>
-    <cellStyle name="ปกติ 13" xfId="39" xr:uid="{5A7A96AB-D851-4B5C-8770-98A5DD705215}"/>
-    <cellStyle name="ปกติ 2" xfId="40" xr:uid="{EF6C27FD-AE59-44FA-A926-676D53635655}"/>
-    <cellStyle name="ปกติ 2 2" xfId="41" xr:uid="{FC5A4DA3-D2E7-4FA5-9F3A-4F4D5EC93428}"/>
-    <cellStyle name="ปกติ 2 3" xfId="42" xr:uid="{CC1D4144-16F7-488D-886F-BAD62878CE26}"/>
-    <cellStyle name="ปกติ 2 4" xfId="43" xr:uid="{3C6F201C-ABD1-4C36-9ED4-F9AB018FE907}"/>
-    <cellStyle name="ปกติ 2 5" xfId="44" xr:uid="{1C1AFCE4-92F6-492E-A1E5-6883A0B92708}"/>
-    <cellStyle name="ปกติ 21" xfId="45" xr:uid="{B8A4D502-9079-4956-8484-C836F1AF4F2C}"/>
-    <cellStyle name="ปกติ 29" xfId="46" xr:uid="{550EB65B-C1EE-4251-9DC0-B09231F56ED3}"/>
-    <cellStyle name="ปกติ 3" xfId="47" xr:uid="{BF0E9128-2F29-41D4-80F6-513C5837A950}"/>
-    <cellStyle name="ปกติ 4" xfId="48" xr:uid="{9265C5AF-3920-47A0-B599-E8EC5B708B96}"/>
-    <cellStyle name="ปกติ 5" xfId="49" xr:uid="{9AAA1EBF-39F0-4809-8C59-B07E8F8B2770}"/>
-    <cellStyle name="ปกติ 6" xfId="50" xr:uid="{3F8652CF-417F-4FDC-9AD0-8D6053DEF649}"/>
-    <cellStyle name="ปกติ 61" xfId="51" xr:uid="{2023A565-4990-4174-BFA5-8DB64AE51D8E}"/>
-    <cellStyle name="ปกติ 7" xfId="52" xr:uid="{0961FB5B-F4B5-4AF7-AC75-BEE29864B0BD}"/>
-    <cellStyle name="ปกติ 8" xfId="53" xr:uid="{C5E6CA5F-DB32-4A49-B4A2-DECE908E958F}"/>
-    <cellStyle name="ปกติ 9" xfId="54" xr:uid="{3005E4B9-4356-4F45-8362-806420418097}"/>
-    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="55" xr:uid="{D9915553-087A-45A2-A836-317568D9C049}"/>
+    <cellStyle name="จุลภาค 2" xfId="35" xr:uid="{C3489436-91AA-4DC4-915D-C62E56FC6D9F}"/>
+    <cellStyle name="ปกติ 10" xfId="36" xr:uid="{E9C23CF5-5C37-46EA-B486-BDF6F504FFC5}"/>
+    <cellStyle name="ปกติ 11" xfId="37" xr:uid="{8135E05C-B4A3-4EAA-ACA0-9B9AAE073FB7}"/>
+    <cellStyle name="ปกติ 12" xfId="38" xr:uid="{ABC11CE9-8172-4CB4-B29A-9AC5FD86B6B6}"/>
+    <cellStyle name="ปกติ 13" xfId="39" xr:uid="{DD6C104B-7E68-455E-BD96-1E073974A5D1}"/>
+    <cellStyle name="ปกติ 2" xfId="40" xr:uid="{2ADDC16E-8324-4596-B9D9-A14404DF4CC1}"/>
+    <cellStyle name="ปกติ 2 2" xfId="41" xr:uid="{DDA76946-CB0E-4572-AC82-68ADE1B9AA20}"/>
+    <cellStyle name="ปกติ 2 3" xfId="42" xr:uid="{349F280D-87D3-4789-B206-FF6AE185AC28}"/>
+    <cellStyle name="ปกติ 2 4" xfId="43" xr:uid="{FF7D8CB5-EB9E-4931-B0F8-C450778EAB12}"/>
+    <cellStyle name="ปกติ 2 5" xfId="44" xr:uid="{30F3CAD0-D8BF-4CC7-9354-77798331CDA0}"/>
+    <cellStyle name="ปกติ 21" xfId="45" xr:uid="{81E929AC-2AB4-43ED-9ECA-C32E26282C53}"/>
+    <cellStyle name="ปกติ 29" xfId="46" xr:uid="{5FC1C8D8-0CC8-4A2C-A789-0FD92D7DE52E}"/>
+    <cellStyle name="ปกติ 3" xfId="47" xr:uid="{FBC057B3-F0C0-47E8-98B5-3ACE55A2E68C}"/>
+    <cellStyle name="ปกติ 4" xfId="48" xr:uid="{DBFC87A0-2C2B-4B4D-BE34-6FD74B14ECA1}"/>
+    <cellStyle name="ปกติ 5" xfId="49" xr:uid="{65C8EDE8-04EF-4E27-9AD3-A8CD5517EF41}"/>
+    <cellStyle name="ปกติ 6" xfId="50" xr:uid="{5B6C5EF2-08FF-4EBA-859A-1E9746B5074B}"/>
+    <cellStyle name="ปกติ 61" xfId="51" xr:uid="{5F70B0E9-F9DB-4BF1-9B61-DA10CC1A0F8C}"/>
+    <cellStyle name="ปกติ 7" xfId="52" xr:uid="{67DBB491-5525-49B6-938E-DDDC633F6440}"/>
+    <cellStyle name="ปกติ 8" xfId="53" xr:uid="{62F83B30-7562-40BF-A2DD-46127E14145B}"/>
+    <cellStyle name="ปกติ 9" xfId="54" xr:uid="{02273414-EFF7-46D2-BDB8-5C7578B408F8}"/>
+    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="55" xr:uid="{3B706ACB-EBF5-45C6-82FF-47F29B90BE25}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1463,7 +1463,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44712E73-2855-430E-BB05-81074C9E3C3B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12E34443-11B0-4D47-B325-91A4A6881042}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -30239,13 +30239,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A19" xr:uid="{87E4E6FB-FC87-4090-A3EE-E3E96C7EF848}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A19" xr:uid="{7630C4D9-6884-480E-8DAD-1344F09CDE1F}">
       <formula1>$A$39:$A$43</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{C32CF4BE-3E15-4DB2-9DFB-E6966CD1A905}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{0B32320C-51B6-4871-AA48-185D5CC978B8}">
       <formula1>$A$61:$A$73</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J19" xr:uid="{34EA3812-8E1B-4265-BE25-56E7B1D218FC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J19" xr:uid="{E755AF46-8DDA-47AF-B73B-8729E41E0B77}">
       <formula1>$A$45:$A$53</formula1>
     </dataValidation>
   </dataValidations>
@@ -30260,7 +30260,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8109160-886B-4ECE-908E-F2C914ABF459}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36152D60-17AA-4BD6-8485-AA9EDA55E756}">
   <dimension ref="A1:B215"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31140,7 +31140,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B26E2019-C399-4AF2-A537-6A488B1FE64E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FBB01F9-1B18-411C-98AA-4775A4CC774B}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>

--- a/docs/templates/B5C3-SHORE.xlsx
+++ b/docs/templates/B5C3-SHORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\build\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3510723D-D2EA-4F52-BD26-88005D4B4695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F295EEAC-0711-4802-8F9B-72BAD49C98A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BEC41915-64B8-47E3-BA14-EAB81BC34DBE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1246588A-1AC1-4697-B8BD-211488A063AD}"/>
   </bookViews>
   <sheets>
     <sheet name="DataImport" sheetId="1" r:id="rId1"/>
@@ -1110,63 +1110,63 @@
     </xf>
   </cellXfs>
   <cellStyles count="57">
-    <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{8B0EA57F-0D5D-45D1-BB7C-C87FD4EE3607}"/>
+    <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{8F6D9BFB-6D89-4B97-BA98-36338551E43B}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="2" xr:uid="{89CAEACC-AF01-4019-B194-052C3970C9DE}"/>
-    <cellStyle name="Normal 10 10" xfId="3" xr:uid="{F6E978AA-63D1-4DDA-858C-82C93E47094C}"/>
-    <cellStyle name="Normal 10 10 2" xfId="4" xr:uid="{A1AFC344-F009-4AF7-A8C5-50E487BFCE1C}"/>
-    <cellStyle name="Normal 10 2 10" xfId="5" xr:uid="{80348091-BFF2-4B18-A805-D9F04D2461AA}"/>
-    <cellStyle name="Normal 12" xfId="6" xr:uid="{22C011E8-828D-491D-8C24-F3CFAF554779}"/>
-    <cellStyle name="Normal 13" xfId="7" xr:uid="{693F8681-0864-4A51-B61E-BB37F142862B}"/>
-    <cellStyle name="Normal 137" xfId="8" xr:uid="{4155318E-2C69-4AD9-9964-63BA8853FD83}"/>
-    <cellStyle name="Normal 14" xfId="9" xr:uid="{8AE7C872-22E2-416B-9353-E44A1311BF7F}"/>
-    <cellStyle name="Normal 15" xfId="10" xr:uid="{F8690C3F-D60F-4C09-84C7-28CF41107BA1}"/>
-    <cellStyle name="Normal 2" xfId="11" xr:uid="{4053F517-9EC3-4FFE-8CBF-CC163C4536A1}"/>
-    <cellStyle name="Normal 2 10" xfId="12" xr:uid="{2E183095-E506-4785-83B9-50096D697240}"/>
-    <cellStyle name="Normal 2 10 2" xfId="13" xr:uid="{1812FCEA-6FBA-4137-95F8-55567A7A78C6}"/>
-    <cellStyle name="Normal 2 10 2 2" xfId="14" xr:uid="{6E404B8B-00CC-48AC-8F4A-EACF78DB68F0}"/>
-    <cellStyle name="Normal 2 2" xfId="15" xr:uid="{D8026C88-4872-4CF8-B591-424B35F3A5E1}"/>
-    <cellStyle name="Normal 2 2 10" xfId="16" xr:uid="{912CB251-B3AB-478A-BAE3-1B7B28290D52}"/>
-    <cellStyle name="Normal 2 2 2" xfId="17" xr:uid="{863E8798-BD73-4BE9-8E2D-46872694ED0C}"/>
-    <cellStyle name="Normal 2 2 3" xfId="18" xr:uid="{D9E409A5-EE3F-4CD8-99A4-412693C8F2B5}"/>
-    <cellStyle name="Normal 2 3" xfId="19" xr:uid="{E5B6B06B-2A66-4E30-AA41-546DE8556F5D}"/>
-    <cellStyle name="Normal 2 4" xfId="20" xr:uid="{3536C0E0-8AE9-4792-940A-27A3C9962908}"/>
-    <cellStyle name="Normal 2 5" xfId="21" xr:uid="{4F2B2949-9BB4-4C1D-A5AA-3E03968CC959}"/>
-    <cellStyle name="Normal 3" xfId="22" xr:uid="{3D15DED5-9DDA-4C6C-AEE1-FFE9F5F9FEF1}"/>
-    <cellStyle name="Normal 3 2" xfId="23" xr:uid="{87A3462D-F019-49DE-8242-70E30C6B38F6}"/>
-    <cellStyle name="Normal 4" xfId="24" xr:uid="{8B940C62-03CC-4EFB-A57B-3172A32BC06E}"/>
-    <cellStyle name="Normal 49" xfId="25" xr:uid="{E0E3CB2E-BDB5-46A6-AA6B-7866EF508A0D}"/>
-    <cellStyle name="Normal 5" xfId="26" xr:uid="{9A60FEEE-6C70-4150-BE41-E069C522050D}"/>
-    <cellStyle name="Normal 53" xfId="27" xr:uid="{D1FFCB0B-0BA6-471E-AB8F-87D04E9EC17D}"/>
-    <cellStyle name="Normal 54" xfId="28" xr:uid="{C6109A46-EB0D-4758-A686-7E8EEE3B837F}"/>
-    <cellStyle name="Normal 6" xfId="29" xr:uid="{E4DB009B-E1DD-446C-A210-D80A61C703B9}"/>
-    <cellStyle name="Normal 7" xfId="30" xr:uid="{A5DE1544-CF1E-4ABE-A486-9D87DAB7B006}"/>
-    <cellStyle name="Normal 71" xfId="31" xr:uid="{A8172EE3-F936-4849-8312-071F6E3562E8}"/>
-    <cellStyle name="Normal 8" xfId="32" xr:uid="{C4BA93D5-8545-4599-BCEE-83636AF27A77}"/>
-    <cellStyle name="Normal 9" xfId="33" xr:uid="{872EF8AB-6407-4835-BB90-DD7FCD2C4E29}"/>
-    <cellStyle name="Normal_CHORE" xfId="34" xr:uid="{C15FECAA-BC3D-4E2E-8E69-8ACC7FB069F4}"/>
+    <cellStyle name="Normal 10" xfId="2" xr:uid="{05414223-9F7B-4CFE-AEFA-2766D0F00587}"/>
+    <cellStyle name="Normal 10 10" xfId="3" xr:uid="{EE363C41-BE52-4E07-A377-997F5F366055}"/>
+    <cellStyle name="Normal 10 10 2" xfId="4" xr:uid="{6901271A-0C1C-40CF-88B8-4C785E3F22A2}"/>
+    <cellStyle name="Normal 10 2 10" xfId="5" xr:uid="{ED25B588-284C-46C8-BC20-C5F05FD1C1AC}"/>
+    <cellStyle name="Normal 12" xfId="6" xr:uid="{B45CB5C2-334E-41FE-9F65-867C091D0FA6}"/>
+    <cellStyle name="Normal 13" xfId="7" xr:uid="{5C1F9817-3E4E-4C87-8A17-7B8AF7603554}"/>
+    <cellStyle name="Normal 137" xfId="8" xr:uid="{A0061AD7-A13A-4933-A725-B696FAEA8B65}"/>
+    <cellStyle name="Normal 14" xfId="9" xr:uid="{B635344E-7954-41B7-B36F-D25610658309}"/>
+    <cellStyle name="Normal 15" xfId="10" xr:uid="{852EA0B5-B84F-48E7-B71A-77C24EF430CC}"/>
+    <cellStyle name="Normal 2" xfId="11" xr:uid="{1EC056BC-4F72-435A-BFDE-F54A7E296402}"/>
+    <cellStyle name="Normal 2 10" xfId="12" xr:uid="{DB5CB36B-4DB9-4C6E-969B-50CFAE7A5B77}"/>
+    <cellStyle name="Normal 2 10 2" xfId="13" xr:uid="{D150D736-8509-4DCD-B16B-FB44CB6C7907}"/>
+    <cellStyle name="Normal 2 10 2 2" xfId="14" xr:uid="{83451157-BDF4-4BF3-A285-82BC11D33F9C}"/>
+    <cellStyle name="Normal 2 2" xfId="15" xr:uid="{A7C03CBD-A5E5-4B19-BF4E-7E032E4C0717}"/>
+    <cellStyle name="Normal 2 2 10" xfId="16" xr:uid="{55420004-1B7C-4F4A-968A-720C97FFDFF7}"/>
+    <cellStyle name="Normal 2 2 2" xfId="17" xr:uid="{42DC022E-4E4D-4A86-81DC-640C7D56434A}"/>
+    <cellStyle name="Normal 2 2 3" xfId="18" xr:uid="{911A081F-8C11-4D6B-A5D9-A4C496A81750}"/>
+    <cellStyle name="Normal 2 3" xfId="19" xr:uid="{D770F7FD-8D81-46F4-9961-C93B7A6A785D}"/>
+    <cellStyle name="Normal 2 4" xfId="20" xr:uid="{183C6551-E5EE-4ABA-8EB0-31281826FEB3}"/>
+    <cellStyle name="Normal 2 5" xfId="21" xr:uid="{3BC0A881-B91B-4065-A818-076FAD6D2E58}"/>
+    <cellStyle name="Normal 3" xfId="22" xr:uid="{24100E04-DDA2-4FDF-813D-5086FE8723F3}"/>
+    <cellStyle name="Normal 3 2" xfId="23" xr:uid="{6EDDDD64-AD69-4EDA-A9EA-ECCA9B77D92E}"/>
+    <cellStyle name="Normal 4" xfId="24" xr:uid="{AF2DFF84-BA18-44D7-B32B-2A16FE89EDD8}"/>
+    <cellStyle name="Normal 49" xfId="25" xr:uid="{D1630283-77AB-4C2C-9930-F40EB826D60D}"/>
+    <cellStyle name="Normal 5" xfId="26" xr:uid="{FD388C05-69EB-4158-9579-15358325B894}"/>
+    <cellStyle name="Normal 53" xfId="27" xr:uid="{44999D14-D986-4AC4-9C12-903D6BD57BFA}"/>
+    <cellStyle name="Normal 54" xfId="28" xr:uid="{D61CE877-8A9F-4C42-9EB4-C18DE8787A7D}"/>
+    <cellStyle name="Normal 6" xfId="29" xr:uid="{F8353376-2353-42E2-B71E-14B4BBDB6E4F}"/>
+    <cellStyle name="Normal 7" xfId="30" xr:uid="{D173C8F9-74AB-4236-B7A3-4C0D50366705}"/>
+    <cellStyle name="Normal 71" xfId="31" xr:uid="{187FB99E-4410-4567-8F66-6B85DA28FB10}"/>
+    <cellStyle name="Normal 8" xfId="32" xr:uid="{7EFB3A54-88F1-4211-9D7C-93004439825D}"/>
+    <cellStyle name="Normal 9" xfId="33" xr:uid="{AC19470E-065F-4009-9166-B84FAAF4F992}"/>
+    <cellStyle name="Normal_CHORE" xfId="34" xr:uid="{A6CE16EC-3BC4-40A8-940D-F35434403BB0}"/>
     <cellStyle name="Percent" xfId="35" builtinId="5"/>
-    <cellStyle name="จุลภาค 2" xfId="36" xr:uid="{6004607A-3CB0-42FB-B4C6-3AE225D2DE3C}"/>
-    <cellStyle name="ปกติ 10" xfId="37" xr:uid="{903ED954-B6D8-4013-96E4-27F751EF9E6E}"/>
-    <cellStyle name="ปกติ 11" xfId="38" xr:uid="{AF8DF4E4-CF20-456E-99FB-81B3DCD27998}"/>
-    <cellStyle name="ปกติ 12" xfId="39" xr:uid="{F9289988-5079-4A93-88F3-82E3D106BB3E}"/>
-    <cellStyle name="ปกติ 13" xfId="40" xr:uid="{62A25D9F-58B1-4CF5-B858-715A463C4828}"/>
-    <cellStyle name="ปกติ 2" xfId="41" xr:uid="{B53A3C09-3376-4223-BA61-8F6289E2C62E}"/>
-    <cellStyle name="ปกติ 2 2" xfId="42" xr:uid="{F9EBED7B-828E-400B-A9C6-E8E02CC6AD3E}"/>
-    <cellStyle name="ปกติ 2 3" xfId="43" xr:uid="{BBCD57E9-810B-43CA-9F76-22E3EF3B53DB}"/>
-    <cellStyle name="ปกติ 2 4" xfId="44" xr:uid="{77DFFFE7-557B-43EB-B4C4-2D53E3EE1EB9}"/>
-    <cellStyle name="ปกติ 2 5" xfId="45" xr:uid="{C051141B-2643-4840-8676-FE379C5E5253}"/>
-    <cellStyle name="ปกติ 21" xfId="46" xr:uid="{78240CEB-7CCE-48F5-A6F7-E554975F5265}"/>
-    <cellStyle name="ปกติ 29" xfId="47" xr:uid="{7448F233-5631-46EF-8AE3-B90D6BF4418F}"/>
-    <cellStyle name="ปกติ 3" xfId="48" xr:uid="{5197AEF2-3031-4578-837F-BB53578ADE1C}"/>
-    <cellStyle name="ปกติ 4" xfId="49" xr:uid="{827DA2A7-C866-4991-B0FB-A6F8A5287E9B}"/>
-    <cellStyle name="ปกติ 5" xfId="50" xr:uid="{EE4DEF71-26CB-41EA-9E04-5F6217894385}"/>
-    <cellStyle name="ปกติ 6" xfId="51" xr:uid="{0F0CBCD4-FAB4-4558-AF85-48FA20BAD982}"/>
-    <cellStyle name="ปกติ 61" xfId="52" xr:uid="{FB91DC48-4AD3-4707-AF87-0756588870BC}"/>
-    <cellStyle name="ปกติ 7" xfId="53" xr:uid="{FE5E663D-D4D9-468D-9F32-6A1487826C4C}"/>
-    <cellStyle name="ปกติ 8" xfId="54" xr:uid="{203C5334-7348-4877-B791-93AE82BD3DCE}"/>
-    <cellStyle name="ปกติ 9" xfId="55" xr:uid="{526EC915-9026-4862-83CA-6368626A2FC9}"/>
-    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="56" xr:uid="{593A90E6-FE79-4C45-B1C4-581F9054769D}"/>
+    <cellStyle name="จุลภาค 2" xfId="36" xr:uid="{15C1009B-A686-4457-81EB-C0C406874F0F}"/>
+    <cellStyle name="ปกติ 10" xfId="37" xr:uid="{EDEC9A8C-67E1-4DEA-953C-629C6A1DEF01}"/>
+    <cellStyle name="ปกติ 11" xfId="38" xr:uid="{3D1C72B2-B5C4-47F6-AB04-DB851A90737A}"/>
+    <cellStyle name="ปกติ 12" xfId="39" xr:uid="{CC7A0E60-1F8A-474A-89D7-8A568D901519}"/>
+    <cellStyle name="ปกติ 13" xfId="40" xr:uid="{BF29541C-919C-48CA-80CA-346DA998A23B}"/>
+    <cellStyle name="ปกติ 2" xfId="41" xr:uid="{83FB10AE-BCC3-47E5-98BA-3036FA27BC8C}"/>
+    <cellStyle name="ปกติ 2 2" xfId="42" xr:uid="{FA42DDAF-7B36-44CC-BEE0-A9BE0673D450}"/>
+    <cellStyle name="ปกติ 2 3" xfId="43" xr:uid="{0DC7D632-039A-4BF5-A279-7DEEEABBC0D6}"/>
+    <cellStyle name="ปกติ 2 4" xfId="44" xr:uid="{4F746C1C-FF12-44ED-91D1-A98575859A3A}"/>
+    <cellStyle name="ปกติ 2 5" xfId="45" xr:uid="{4933EB41-82C0-41B8-A1EB-201AC1D6E6B6}"/>
+    <cellStyle name="ปกติ 21" xfId="46" xr:uid="{202BFE84-68B9-4AE4-B95B-319A1D8FAFA6}"/>
+    <cellStyle name="ปกติ 29" xfId="47" xr:uid="{23CC98EC-A9F3-4BA4-82AF-03BB734A9DB5}"/>
+    <cellStyle name="ปกติ 3" xfId="48" xr:uid="{FC510F88-715A-456A-98C2-FBDCF0C2F7D9}"/>
+    <cellStyle name="ปกติ 4" xfId="49" xr:uid="{0AAF8224-CB8F-43A8-8855-2769D2B3C7BE}"/>
+    <cellStyle name="ปกติ 5" xfId="50" xr:uid="{A9B225F9-700C-4EC0-86A7-82AF93AFFAB5}"/>
+    <cellStyle name="ปกติ 6" xfId="51" xr:uid="{ECD13629-1AF7-4864-B7F5-D7D000C54BAA}"/>
+    <cellStyle name="ปกติ 61" xfId="52" xr:uid="{1ECCA3C0-307D-465F-811C-23878080EFE3}"/>
+    <cellStyle name="ปกติ 7" xfId="53" xr:uid="{AFB39DD3-DE7F-46DC-819C-829EB13D2B53}"/>
+    <cellStyle name="ปกติ 8" xfId="54" xr:uid="{A676EBC1-BBE9-4960-889F-37C0E5CA6AAB}"/>
+    <cellStyle name="ปกติ 9" xfId="55" xr:uid="{48B4B20C-BA7D-4726-A398-BF5B3E33BA4C}"/>
+    <cellStyle name="ปกติ_EXP. BOOKING.1" xfId="56" xr:uid="{CFBC67E0-E5AF-4E62-ADBD-E4C9C059813D}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1488,7 +1488,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9DD6D04-2AF8-42E0-94A9-05537342418B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E8A00F9-C267-4F8A-9E06-9DD99DBDAE9E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -30154,13 +30154,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A19" xr:uid="{FA253564-D098-4ADF-B0BE-1F9FB2700CAF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A19" xr:uid="{0EE50BBF-71F9-4959-B6AC-49EF18823FB8}">
       <formula1>$A$34:$A$38</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{693DA56F-89D9-4B7B-B203-C9E28BE75B55}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{A39A30E0-2B61-4D4E-B275-7558BFF736DE}">
       <formula1>$A$56:$A$68</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J19" xr:uid="{3D3B86B1-F256-4DF7-9464-F72BFEE367D8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J19" xr:uid="{F23BE250-4C79-4AF2-ACE2-DE562E6C0D0D}">
       <formula1>$A$40:$A$48</formula1>
     </dataValidation>
   </dataValidations>
@@ -30175,7 +30175,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EE64445-A6BF-4A9A-BFFA-7C7976D12C39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA68B87B-DDDA-4343-8893-335AF1053E62}">
   <dimension ref="A1:B215"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31055,7 +31055,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29AF216C-4323-4700-BEF1-9949E33181BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC962E9-3D5E-4B6E-A3D4-AB5EE9B7EE5F}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
